--- a/data/trans_bre/P19C04-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C04-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 1,15</t>
+          <t>-7,79; 0,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 4,36</t>
+          <t>-6,12; 3,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 3,26</t>
+          <t>-4,97; 3,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 1,06</t>
+          <t>-10,23; 1,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-54,49; 14,53</t>
+          <t>-58,21; 10,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,09; 40,19</t>
+          <t>-37,62; 34,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,25; 49,78</t>
+          <t>-43,07; 59,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-83,57; 44,82</t>
+          <t>-81,36; 43,3</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 0,91</t>
+          <t>-7,3; 1,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,74; -2,52</t>
+          <t>-10,89; -2,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 1,89</t>
+          <t>-6,66; 1,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 1,12</t>
+          <t>-8,3; 0,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,09; 8,39</t>
+          <t>-44,63; 10,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,61; -13,92</t>
+          <t>-51,88; -16,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,06; 16,36</t>
+          <t>-39,55; 16,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,26; 13,47</t>
+          <t>-62,87; 9,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,09; -1,15</t>
+          <t>-9,7; -1,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,85; -4,04</t>
+          <t>-12,88; -4,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 0,04</t>
+          <t>-7,44; 0,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 0,53</t>
+          <t>-6,2; 0,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,66; -6,22</t>
+          <t>-46,93; -7,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,82; -19,6</t>
+          <t>-50,75; -19,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,19; 0,54</t>
+          <t>-46,16; 0,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,3; 5,98</t>
+          <t>-45,6; 4,96</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,24; -1,42</t>
+          <t>-13,38; -0,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,11; -1,78</t>
+          <t>-12,07; -1,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,24; -1,62</t>
+          <t>-10,69; -2,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 5,2</t>
+          <t>-6,33; 5,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,17; -6,04</t>
+          <t>-43,98; -3,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,55; -7,75</t>
+          <t>-43,36; -3,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,76; -10,24</t>
+          <t>-52,13; -12,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 90,11</t>
+          <t>-42,32; 111,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 0,13</t>
+          <t>-12,9; 0,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,74; -2,55</t>
+          <t>-16,38; -2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,03; -7,84</t>
+          <t>-19,76; -7,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,26; -2,39</t>
+          <t>-9,71; -2,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-44,68; 1,22</t>
+          <t>-43,71; 3,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,78; -8,81</t>
+          <t>-47,15; -9,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-65,9; -32,41</t>
+          <t>-64,33; -31,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,7; -12,83</t>
+          <t>-43,88; -12,48</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,85; -1,82</t>
+          <t>-16,97; -1,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,08; -7,37</t>
+          <t>-22,83; -6,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,71; -2,11</t>
+          <t>-16,83; -1,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,3; -6,3</t>
+          <t>-22,44; -5,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,52; -7,28</t>
+          <t>-51,57; -7,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,34; -21,54</t>
+          <t>-53,2; -18,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-54,11; -9,3</t>
+          <t>-53,31; -5,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,45; -27,34</t>
+          <t>-83,53; -26,94</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 1,01</t>
+          <t>-17,0; 1,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,41; -4,28</t>
+          <t>-22,52; -3,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 6,93</t>
+          <t>-12,82; 6,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,8; -1,58</t>
+          <t>-11,03; -1,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,8; 6,3</t>
+          <t>-56,18; 8,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,51; -12,38</t>
+          <t>-48,61; -9,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 30,98</t>
+          <t>-38,18; 27,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,39; -6,34</t>
+          <t>-38,6; -5,55</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -3,19</t>
+          <t>-7,22; -3,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,28; -4,76</t>
+          <t>-9,4; -4,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -3,01</t>
+          <t>-6,92; -3,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,13; -0,7</t>
+          <t>-6,44; -1,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,32; -17,24</t>
+          <t>-34,5; -17,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,81; -20,37</t>
+          <t>-35,84; -21,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,62; -17,67</t>
+          <t>-36,4; -17,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,83; -8,22</t>
+          <t>-40,93; -10,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C04-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C04-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,53</t>
+          <t>-3,64</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-47,47%</t>
+          <t>-45,7%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 0,91</t>
+          <t>-7,54; 1,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 3,86</t>
+          <t>-5,85; 3,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 3,78</t>
+          <t>-4,78; 3,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 1,2</t>
+          <t>-10,08; 1,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,21; 10,47</t>
+          <t>-57,3; 12,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,62; 34,7</t>
+          <t>-36,53; 33,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 59,39</t>
+          <t>-41,73; 50,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-81,36; 43,3</t>
+          <t>-79,82; 41,17</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,66</t>
+          <t>-2,74</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-32,92%</t>
+          <t>-23,21%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 1,13</t>
+          <t>-7,27; 0,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,89; -2,77</t>
+          <t>-10,83; -2,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 1,85</t>
+          <t>-6,5; 1,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 0,87</t>
+          <t>-7,77; 1,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,63; 10,23</t>
+          <t>-45,0; 6,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,88; -16,22</t>
+          <t>-51,84; -15,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,55; 16,49</t>
+          <t>-39,64; 17,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,87; 9,25</t>
+          <t>-50,12; 18,81</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,88</t>
+          <t>-4,7</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-24,9%</t>
+          <t>-34,26%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,7; -1,21</t>
+          <t>-9,77; -1,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,88; -4,14</t>
+          <t>-12,91; -4,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 0,01</t>
+          <t>-7,7; -0,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,38</t>
+          <t>-8,24; -1,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,93; -7,7</t>
+          <t>-47,34; -9,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,75; -19,74</t>
+          <t>-50,98; -20,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 0,39</t>
+          <t>-46,53; 0,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-45,6; 4,96</t>
+          <t>-50,63; -10,38</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>-5,59</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-11,09%</t>
+          <t>-36,74%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,38; -0,95</t>
+          <t>-13,56; -1,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,07; -1,1</t>
+          <t>-11,49; -1,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,69; -2,08</t>
+          <t>-10,54; -1,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 5,46</t>
+          <t>-8,63; -2,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,98; -3,84</t>
+          <t>-44,04; -6,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,36; -3,71</t>
+          <t>-41,67; -5,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,13; -12,18</t>
+          <t>-51,46; -9,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,32; 111,31</t>
+          <t>-50,73; -17,6</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,93</t>
+          <t>-6,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-29,91%</t>
+          <t>-32,84%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 0,5</t>
+          <t>-12,69; 1,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,38; -2,66</t>
+          <t>-16,01; -2,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,76; -7,77</t>
+          <t>-19,5; -7,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,71; -2,2</t>
+          <t>-10,78; -2,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,71; 3,14</t>
+          <t>-42,07; 7,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,15; -9,43</t>
+          <t>-45,77; -9,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-64,33; -31,57</t>
+          <t>-65,01; -30,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-43,88; -12,48</t>
+          <t>-45,9; -14,96</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-12,81</t>
+          <t>-7,04</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-54,86%</t>
+          <t>-30,86%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -1,88</t>
+          <t>-17,78; -1,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,83; -6,49</t>
+          <t>-22,62; -6,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,83; -1,46</t>
+          <t>-16,37; -1,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,44; -5,79</t>
+          <t>-11,46; -2,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,57; -7,79</t>
+          <t>-50,53; -6,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,2; -18,89</t>
+          <t>-52,29; -19,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,31; -5,84</t>
+          <t>-52,35; -6,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,53; -26,94</t>
+          <t>-45,24; -13,21</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,97</t>
+          <t>-5,81</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-23,54%</t>
+          <t>-23,52%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 1,62</t>
+          <t>-18,46; 1,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,52; -3,2</t>
+          <t>-21,97; -3,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 6,22</t>
+          <t>-12,01; 6,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,03; -1,19</t>
+          <t>-11,16; -1,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-56,18; 8,84</t>
+          <t>-58,37; 13,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,61; -9,37</t>
+          <t>-48,56; -11,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 27,75</t>
+          <t>-36,33; 29,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,6; -5,55</t>
+          <t>-39,04; -5,99</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-4,86</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-27,28%</t>
+          <t>-29,71%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -3,2</t>
+          <t>-7,41; -3,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -4,93</t>
+          <t>-9,42; -5,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -3,01</t>
+          <t>-6,86; -2,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,44; -1,1</t>
+          <t>-6,35; -3,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,5; -17,02</t>
+          <t>-34,97; -16,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,84; -21,28</t>
+          <t>-36,04; -21,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,4; -17,75</t>
+          <t>-36,39; -17,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,93; -10,96</t>
+          <t>-36,63; -21,18</t>
         </is>
       </c>
     </row>
